--- a/Luban/DataTables/Datas/Ability/技能表.xlsx
+++ b/Luban/DataTables/Datas/Ability/技能表.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -60,6 +60,9 @@
     <t>addressable</t>
   </si>
   <si>
+    <t>abilityType</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
   </si>
   <si>
     <t>地址</t>
+  </si>
+  <si>
+    <t>技能类型</t>
   </si>
   <si>
     <t>##comment</t>
@@ -78,7 +84,15 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">通用技能
+武器技能
+</t>
+  </si>
+  <si>
     <t>Ability/Weapon/A_Sword_01_NormalAtk.asset</t>
+  </si>
+  <si>
+    <t>武器技能</t>
   </si>
   <si>
     <t>Ability/Weapon/A_CrossBow_01_NormalAtk.asset</t>
@@ -742,7 +756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -760,10 +774,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1092,15 +1115,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="25.8583333333333" customWidth="1"/>
     <col min="3" max="3" width="48.3583333333333" customWidth="1"/>
+    <col min="4" max="4" width="14.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:3">
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1110,79 +1134,111 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" ht="58.5" spans="1:3">
+    <row r="2" ht="58.5" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="71.25" spans="1:3">
+    <row r="3" s="2" customFormat="1" ht="71.25" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:3">
+    <row r="4" s="2" customFormat="1" spans="1:4">
       <c r="A4" s="4"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
+    <row r="5" spans="1:4">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10">
         <v>100001</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>8</v>
+      <c r="C5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8">
+    <row r="6" spans="1:4">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10">
         <v>100002</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>9</v>
+      <c r="C6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="B7" s="8">
+    <row r="7" spans="1:4">
+      <c r="B7" s="10">
         <v>100003</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>10</v>
+      <c r="C7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+    <row r="8" spans="1:4">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
     </row>
-    <row r="9" spans="1:3">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+    <row r="9" spans="1:4">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11"/>
     </row>
-    <row r="10" spans="1:3">
-      <c r="B10" s="8">
+    <row r="10" spans="1:4">
+      <c r="B10" s="10">
         <v>200000</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>11</v>
+      <c r="C10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="B13" s="8">
+    <row r="11" spans="1:4">
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" s="10">
         <v>300000</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Luban/DataTables/Datas/Ability/技能表.xlsx
+++ b/Luban/DataTables/Datas/Ability/技能表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
+    <workbookView windowWidth="28800" windowHeight="11775" tabRatio="610"/>
   </bookViews>
   <sheets>
     <sheet name="技能表" sheetId="3" r:id="rId1"/>

--- a/Luban/DataTables/Datas/Ability/技能表.xlsx
+++ b/Luban/DataTables/Datas/Ability/技能表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775" tabRatio="610"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
   </bookViews>
   <sheets>
     <sheet name="技能表" sheetId="3" r:id="rId1"/>
